--- a/product_selector_out/STM32H503.xlsx
+++ b/product_selector_out/STM32H503.xlsx
@@ -3196,9 +3196,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="9" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="9" t="inlineStr">
@@ -3870,9 +3870,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="9" t="inlineStr">
@@ -4207,9 +4207,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4428,19 +4428,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32H503KB</t>
+          <t>STM32H503EB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4516,19 +4516,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4538,19 +4538,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32H503CB</t>
+          <t>STM32H503KB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4604,19 +4604,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 33. Peripheral current consumption in Sleep mode</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4626,19 +4626,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4648,19 +4648,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32H503RB</t>
+          <t>STM32H503CB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>
       </c>
     </row>
@@ -4682,15 +4682,103 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32H503RB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32H503RB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 16. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32H503RB</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 16. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32H503RB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Table 33. Peripheral current consumption in Sleep mode</t>
         </is>

--- a/product_selector_out/STM32H503.xlsx
+++ b/product_selector_out/STM32H503.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO15"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.671875" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
@@ -2349,12 +2371,17 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h503cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2377,12 +2404,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -2397,9 +2426,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -2439,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO15"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2509,6 +2537,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2852,6 +2881,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -2949,6 +2983,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3281,7 +3316,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3618,7 +3658,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3955,7 +4000,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4292,7 +4342,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4300,8 +4355,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
